--- a/Link.xlsx
+++ b/Link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test_Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2668B635-0FAB-4B83-98B9-1A1E278E1A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1138185B-BEB5-4F29-93A3-24C5F5E0A79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7253C16-DA96-453E-8E32-644ABBD13F06}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>IMPORTANT LINK</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>pic c</t>
+  </si>
+  <si>
+    <t>getintopc.com</t>
+  </si>
+  <si>
+    <t>software</t>
   </si>
 </sst>
 </file>
@@ -465,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74949BBD-A521-483A-8FF7-929D54218452}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="8.7265625" style="1"/>
@@ -612,14 +618,27 @@
       </c>
       <c r="L15" s="4"/>
     </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="K19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B10:G11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K11:L11"/>
+  <mergeCells count="15">
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K19:L19"/>
     <mergeCell ref="I3:N4"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="B3:H4"/>
@@ -627,6 +646,12 @@
     <mergeCell ref="B6:G7"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K6:L7"/>
+    <mergeCell ref="B14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="B10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K11:L11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{4A406189-9DEF-4090-BB71-2F9BF115C61A}"/>
